--- a/src/test/resources/env/feature-05/data/UsersList.xlsx
+++ b/src/test/resources/env/feature-05/data/UsersList.xlsx
@@ -1,309 +1,183 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7500"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="20490" windowHeight="7500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="UIUsers" sheetId="1" r:id="rId1"/>
-    <sheet name="APIUsers" sheetId="2" r:id="rId2"/>
+    <sheet name="Users" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="APIUsers" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="36">
-  <si>
-    <t>username</t>
-  </si>
-  <si>
-    <t>password</t>
-  </si>
-  <si>
-    <t>webapi1</t>
-  </si>
-  <si>
-    <t>Default1@</t>
-  </si>
-  <si>
-    <t>webapi2</t>
-  </si>
-  <si>
-    <t>webapi3</t>
-  </si>
-  <si>
-    <t>webapi4</t>
-  </si>
-  <si>
-    <t>webapi5</t>
-  </si>
-  <si>
-    <t>webapi6</t>
-  </si>
-  <si>
-    <t>webapi7</t>
-  </si>
-  <si>
-    <t>webapi8</t>
-  </si>
-  <si>
-    <t>webapi9</t>
-  </si>
-  <si>
-    <t>webapi10</t>
-  </si>
-  <si>
-    <t>webui1</t>
-  </si>
-  <si>
-    <t>webui2</t>
-  </si>
-  <si>
-    <t>webui3</t>
-  </si>
-  <si>
-    <t>webui4</t>
-  </si>
-  <si>
-    <t>webui5</t>
-  </si>
-  <si>
-    <t>webui6</t>
-  </si>
-  <si>
-    <t>webui7</t>
-  </si>
-  <si>
-    <t>webui8</t>
-  </si>
-  <si>
-    <t>webui9</t>
-  </si>
-  <si>
-    <t>webui10</t>
-  </si>
-  <si>
-    <t>aranibarman</t>
-  </si>
-  <si>
-    <t>ab</t>
-  </si>
-  <si>
-    <t>arn</t>
-  </si>
-  <si>
-    <t>mkundu</t>
-  </si>
-  <si>
-    <t>mk</t>
-  </si>
-  <si>
-    <t>APIKey</t>
-  </si>
-  <si>
-    <t>Usage</t>
-  </si>
-  <si>
-    <t>BafKFhoBkiz/4IlOWbv+NQSrWMYoAEFYpQ4+ok6ltPQX+eZWi3AOUehjWTS0ecBmcZffqtbahgRlcnELwvDeWg==</t>
-  </si>
-  <si>
-    <t>All</t>
-  </si>
-  <si>
-    <t>Su6abDMoyH4QlsaUQOptYDKiheVo6EROv5fFmXNSAIR4scMKCHuDRp/REq3tGC/e/gUpx1kWFmGqS62cYy8Lvg==</t>
-  </si>
-  <si>
-    <t>OMS APP</t>
-  </si>
-  <si>
-    <t>1F42y2YDCegEvelxbdrwAv6Z9QrzM80PLjli77HS1MD8mwxB2WFTOrBFP36uHf+V0WfFNPUVpaCQJ5wsoBo3MQ==</t>
-  </si>
-  <si>
-    <t>POS APP</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
+      <color rgb="FF006100"/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color rgb="FF9C0006"/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
+      <color rgb="FF9C6500"/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <color theme="0"/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -603,159 +477,159 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1001,7 +875,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -1010,7 +884,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -1023,11 +897,74 @@
       <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1279,256 +1216,612 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:B24"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D24"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.142857142857141" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.2190476190476" style="1" customWidth="1"/>
+    <col width="13" customWidth="1" style="1" min="1" max="1"/>
+    <col width="11.2190476190476" customWidth="1" style="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>27</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>username</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>password</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>usertype</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>logintype</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>webapi1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Default1@</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>[UI, WEBAPI]</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ERP</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>webapi2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Default1@</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[UI, WEBAPI]</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ERP</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>webapi3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>webapi3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[UI, WEBAPI]</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ERP</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>webapi4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Default1@</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[UI, WEBAPI]</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ERP</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>webapi5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Default1@</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[UI, WEBAPI]</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ERP</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>webapi6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Default1@</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[UI, WEBAPI]</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ERP</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>webapi7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Default1@</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[UI, WEBAPI]</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ERP</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>webapi8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Default1@</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[UI, WEBAPI]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ERP</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>webapi9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Default1@</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[UI, WEBAPI]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ERP</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>webapi10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Default1@</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[UI, WEBAPI]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ERP</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>webui1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Default1@</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[UI]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ERP</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>webui2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Default1@</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[UI]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ERP</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>webui3</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Default1@</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[UI]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ERP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>webui4</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Default1@</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[UI]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ERP</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>webui5</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Default1@</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[UI]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ERP</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>webui6</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Default1@</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[UI]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ERP</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>webui7</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Default1@</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[UI]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ERP</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>webui8</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Default1@</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[UI]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ERP</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>webui9</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Default1@</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[UI]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ERP</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>webui10</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Default1@</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[UI]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ERP</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>aranibarman</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ab</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[UI]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ERP</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>arn</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>arn</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[UI]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ERP</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>mkundu</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>mk</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[UI]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ERP</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="3" outlineLevelCol="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.142857142857141" defaultRowHeight="15" outlineLevelRow="3"/>
   <cols>
-    <col min="1" max="1" width="108" customWidth="1"/>
+    <col width="108" customWidth="1" style="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" t="s">
-        <v>35</v>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>APIKey</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>BafKFhoBkiz/4IlOWbv+NQSrWMYoAEFYpQ4+ok6ltPQX+eZWi3AOUehjWTS0ecBmcZffqtbahgRlcnELwvDeWg==</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>Su6abDMoyH4QlsaUQOptYDKiheVo6EROv5fFmXNSAIR4scMKCHuDRp/REq3tGC/e/gUpx1kWFmGqS62cYy8Lvg==</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>OMS APP</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>1F42y2YDCegEvelxbdrwAv6Z9QrzM80PLjli77HS1MD8mwxB2WFTOrBFP36uHf+V0WfFNPUVpaCQJ5wsoBo3MQ==</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>POS APP</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>